--- a/Project tracker/Project tracker.xlsx
+++ b/Project tracker/Project tracker.xlsx
@@ -1,13 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\final_capstone_proj\Capstone project\Project tracker\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6640132-034A-4410-A52F-1415F5C9EBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Project Tracker" sheetId="1" r:id="rId4"/>
+    <sheet name="Project Tracker" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="/bg5iREBxeg2Nqp6gWPkxrtYJYKd6sVMr20hWON7pNg="/>
     </ext>
@@ -16,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
   <si>
     <t>MediAssist AI Capstone Project Tracker</t>
   </si>
@@ -181,38 +193,41 @@
   </si>
   <si>
     <t>Final submission package</t>
+  </si>
+  <si>
+    <t>In Progress</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="24.0"/>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -222,7 +237,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -232,7 +247,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -246,39 +267,42 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="9" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="10" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -468,401 +492,407 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H1000"/>
+  <sheetFormatPr defaultColWidth="11.23046875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="6.33"/>
-    <col customWidth="1" min="2" max="2" width="29.11"/>
-    <col customWidth="1" min="3" max="3" width="59.78"/>
-    <col customWidth="1" min="4" max="4" width="32.67"/>
-    <col customWidth="1" min="5" max="5" width="8.78"/>
-    <col customWidth="1" min="6" max="6" width="10.44"/>
-    <col customWidth="1" min="7" max="7" width="9.44"/>
-    <col customWidth="1" min="8" max="8" width="10.67"/>
-    <col customWidth="1" min="9" max="26" width="10.56"/>
+    <col min="1" max="1" width="6.3046875" customWidth="1"/>
+    <col min="2" max="2" width="29.07421875" customWidth="1"/>
+    <col min="3" max="3" width="59.765625" customWidth="1"/>
+    <col min="4" max="4" width="32.69140625" customWidth="1"/>
+    <col min="5" max="5" width="8.765625" customWidth="1"/>
+    <col min="6" max="6" width="10.4609375" customWidth="1"/>
+    <col min="7" max="7" width="9.4609375" customWidth="1"/>
+    <col min="8" max="8" width="10.69140625" customWidth="1"/>
+    <col min="9" max="26" width="10.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>0.05</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A15" s="2">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="5">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A16" s="2">
         <v>14</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="B16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="5">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="E4" s="5">
+      <c r="B17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="4">
         <v>0.05</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.025</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="3">
-        <v>14.0</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.025</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -1835,9 +1865,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Project tracker/Project tracker.xlsx
+++ b/Project tracker/Project tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\final_capstone_proj\Capstone project\Project tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6640132-034A-4410-A52F-1415F5C9EBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5ED0CA-8DE0-4B1A-AF7A-B065D51E85A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
   <si>
     <t>MediAssist AI Capstone Project Tracker</t>
   </si>
@@ -195,7 +195,10 @@
     <t>Final submission package</t>
   </si>
   <si>
-    <t>In Progress</t>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>In progress</t>
   </si>
 </sst>
 </file>
@@ -588,8 +591,8 @@
       <c r="E4" s="4">
         <v>0.05</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
+      <c r="F4" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -610,8 +613,8 @@
       <c r="E5" s="4">
         <v>0.1</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
+      <c r="F5" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -632,8 +635,8 @@
       <c r="E6" s="4">
         <v>0.05</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
+      <c r="F6" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -655,7 +658,7 @@
         <v>0.1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
